--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0025.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0025.xlsx
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
